--- a/Backend/ordr_project/media/Generated_ORDR_Sheet.xlsx
+++ b/Backend/ordr_project/media/Generated_ORDR_Sheet.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,16 +604,16 @@
         <v>881</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6710676590</v>
+        <v>6710146722</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>16M109</t>
+          <t>16M058</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -666,16 +666,16 @@
         <v>881</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6710676666</v>
+        <v>6710169141</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>16M109</t>
+          <t>16M058</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -728,16 +728,16 @@
         <v>881</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6710676502</v>
+        <v>6710919707</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>16M109</t>
+          <t>16M116</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -790,16 +790,16 @@
         <v>881</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6710671067</v>
+        <v>6710919708</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>16M011</t>
+          <t>16M116</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -852,16 +852,16 @@
         <v>881</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6710671076</v>
+        <v>6710919709</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>16M011</t>
+          <t>16M116</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -914,16 +914,16 @@
         <v>881</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>6710671056</v>
+        <v>6710676666</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>16M011</t>
+          <t>16M109</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -976,16 +976,16 @@
         <v>881</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6710671028</v>
+        <v>6710676372</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>16M011</t>
+          <t>16M109</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1038,16 +1038,16 @@
         <v>881</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>6710671159</v>
+        <v>6710176670</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>16M011</t>
+          <t>16M107</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1100,16 +1100,16 @@
         <v>881</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6710146722</v>
+        <v>6710176629</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>16M058</t>
+          <t>16M107</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1162,16 +1162,16 @@
         <v>881</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>6710146702</v>
+        <v>6710270663</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>16M058</t>
+          <t>16M107</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1224,16 +1224,16 @@
         <v>881</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>6710169141</v>
+        <v>6710269800</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>16M058</t>
+          <t>16M107</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1286,16 +1286,16 @@
         <v>881</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>6710176646</v>
+        <v>6710671056</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>16M107</t>
+          <t>16M011</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1348,16 +1348,16 @@
         <v>881</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6710403207</v>
+        <v>6710671044</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>16M107</t>
+          <t>16M011</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1410,16 +1410,16 @@
         <v>881</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>6710711106</v>
+        <v>6710711134</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1472,16 +1472,16 @@
         <v>881</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6710711107</v>
+        <v>6710931369</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241009</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>16M110</t>
+          <t>16M124</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>To Pay</t>
+          <t>ToPay</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1516,68 +1516,6 @@
         <v>3</v>
       </c>
       <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>dDocument_Items</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>881</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>6710587758</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>20241001</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>20241001</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>20241031</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>16M010</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>To Pay</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Spare</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
